--- a/ОИИ/4 (Функции принадлежностей, прямые графики).xlsx
+++ b/ОИИ/4 (Функции принадлежностей, прямые графики).xlsx
@@ -85,47 +85,611 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Лист1!$A$2:$A$14</c:f>
+              <c:f>Лист1!$A$2:$A$202</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="80">
                   <c:v>180</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="81">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>190</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="91">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="100">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="101">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>210</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="111">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="120">
                   <c:v>220</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="121">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>230</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="131">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>240</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="141">
+                  <c:v>241</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>247</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="151">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>258</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>259</c:v>
+                </c:pt>
+                <c:pt idx="160">
                   <c:v>260</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="161">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>263</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>269</c:v>
+                </c:pt>
+                <c:pt idx="170">
                   <c:v>270</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="171">
+                  <c:v>271</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>277</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>279</c:v>
+                </c:pt>
+                <c:pt idx="180">
                   <c:v>280</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="181">
+                  <c:v>281</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>283</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>284</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>287</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>289</c:v>
+                </c:pt>
+                <c:pt idx="190">
                   <c:v>290</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="191">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>292</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>293</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>294</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>296</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>299</c:v>
+                </c:pt>
+                <c:pt idx="200">
                   <c:v>300</c:v>
                 </c:pt>
               </c:numCache>
@@ -133,47 +697,611 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$B$2:$B$14</c:f>
+              <c:f>Лист1!$B$2:$B$202</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.07000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>0.17</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="91">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.28</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="100">
                   <c:v>0.33</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="101">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="111">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.55</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.57</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.58</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="120">
                   <c:v>0.67</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="121">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>0.83</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="131">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="141">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>0.83</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="151">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="160">
                   <c:v>0.67</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="161">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.58</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.57</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.55</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="170">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="171">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="180">
                   <c:v>0.33</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="181">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.28</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="190">
                   <c:v>0.17</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="191">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.07000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="200">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -245,89 +1373,1223 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Лист1!$A$19:$A$30</c:f>
+              <c:f>Лист1!$A$205:$A$405</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>160</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="61">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>170</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="71">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="80">
                   <c:v>180</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="81">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>190</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="91">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="100">
                   <c:v>200</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="101">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>210</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="111">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="120">
                   <c:v>220</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="121">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>230</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="131">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>240</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="141">
+                  <c:v>241</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>247</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="151">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>258</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>259</c:v>
+                </c:pt>
+                <c:pt idx="160">
                   <c:v>260</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="161">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>263</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>269</c:v>
+                </c:pt>
+                <c:pt idx="170">
                   <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>271</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>277</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>279</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>281</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>283</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>284</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>287</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>289</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>292</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>293</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>294</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>296</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>299</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$B$19:$B$30</c:f>
+              <c:f>Лист1!$B$205:$B$405</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="71">
+                  <c:v>0.55</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="80">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="81">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="82">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="83">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.9399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>0.86</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="111">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.8100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="120">
                   <c:v>0.71</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="121">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.6899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>0.57</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="131">
+                  <c:v>0.5600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>0.43</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="141">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>0.29</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="151">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="160">
                   <c:v>0.14</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="161">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.07000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="200">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -399,84 +2661,1224 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Лист1!$A$36:$A$46</c:f>
+              <c:f>Лист1!$A$408:$A$608</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>110</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="21">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>130</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="31">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>140</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="41">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="50">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="51">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>160</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="61">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>170</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="71">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="80">
                   <c:v>180</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="81">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>190</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="91">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="100">
                   <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>217</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>226</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>241</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>247</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>258</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>259</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>263</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>269</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>271</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>277</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>279</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>281</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>283</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>284</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>287</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>289</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>292</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>293</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>294</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>296</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>297</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>299</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$B$36:$B$46</c:f>
+              <c:f>Лист1!$B$408:$B$608</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
-                  <c:v>0.57</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.78</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9399999999999999</c:v>
+                  <c:v>0.03</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.28</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.58</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.9399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.78</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.57</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="30">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.58</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="45">
                   <c:v>0.37</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.21</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.11</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="46">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.28</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.14</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -564,13 +3966,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>203</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>217</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -594,13 +3996,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>406</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>420</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -908,7 +4310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B608"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -921,7 +4323,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -929,111 +4331,135 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>190</v>
+        <v>101</v>
       </c>
       <c r="B3">
-        <v>0.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="B4">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="B5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>220</v>
+        <v>104</v>
       </c>
       <c r="B6">
-        <v>0.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="B7">
-        <v>0.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>250</v>
+        <v>107</v>
       </c>
       <c r="B9">
-        <v>0.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>260</v>
+        <v>108</v>
       </c>
       <c r="B10">
-        <v>0.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>270</v>
+        <v>109</v>
       </c>
       <c r="B11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="B12">
-        <v>0.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="B13">
-        <v>0.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>300</v>
+        <v>112</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>113</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>114</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>115</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1</v>
+      <c r="A18">
+        <v>116</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1041,186 +4467,4698 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="B20">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>180</v>
+        <v>119</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>210</v>
+        <v>122</v>
       </c>
       <c r="B24">
-        <v>0.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>220</v>
+        <v>123</v>
       </c>
       <c r="B25">
-        <v>0.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="B26">
-        <v>0.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="B27">
-        <v>0.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>250</v>
+        <v>126</v>
       </c>
       <c r="B28">
-        <v>0.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="B29">
-        <v>0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>270</v>
+        <v>128</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
     </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>129</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>130</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>131</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>132</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1</v>
+      <c r="A35">
+        <v>133</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="B36">
-        <v>0.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B37">
-        <v>0.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B38">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B40">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B41">
-        <v>0.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B42">
-        <v>0.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="B43">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="B44">
-        <v>0.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="B45">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
+        <v>144</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>145</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>146</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>147</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>148</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>149</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>150</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>151</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>152</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>153</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>154</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>155</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>156</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>157</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>158</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>159</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>160</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>161</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>162</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>163</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>164</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>165</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>166</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>167</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>168</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>169</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>170</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>171</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>172</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>173</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>174</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>175</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>176</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>177</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>178</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>179</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>180</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>181</v>
+      </c>
+      <c r="B83">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>182</v>
+      </c>
+      <c r="B84">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>183</v>
+      </c>
+      <c r="B85">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>184</v>
+      </c>
+      <c r="B86">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>185</v>
+      </c>
+      <c r="B87">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>186</v>
+      </c>
+      <c r="B88">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>187</v>
+      </c>
+      <c r="B89">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>188</v>
+      </c>
+      <c r="B90">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>189</v>
+      </c>
+      <c r="B91">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>190</v>
+      </c>
+      <c r="B92">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>191</v>
+      </c>
+      <c r="B93">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>192</v>
+      </c>
+      <c r="B94">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>193</v>
+      </c>
+      <c r="B95">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>194</v>
+      </c>
+      <c r="B96">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>195</v>
+      </c>
+      <c r="B97">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>196</v>
+      </c>
+      <c r="B98">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>197</v>
+      </c>
+      <c r="B99">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>198</v>
+      </c>
+      <c r="B100">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>199</v>
+      </c>
+      <c r="B101">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
         <v>200</v>
       </c>
-      <c r="B46">
+      <c r="B102">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>201</v>
+      </c>
+      <c r="B103">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>202</v>
+      </c>
+      <c r="B104">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>203</v>
+      </c>
+      <c r="B105">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>204</v>
+      </c>
+      <c r="B106">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>205</v>
+      </c>
+      <c r="B107">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>206</v>
+      </c>
+      <c r="B108">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>207</v>
+      </c>
+      <c r="B109">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>208</v>
+      </c>
+      <c r="B110">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>209</v>
+      </c>
+      <c r="B111">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>210</v>
+      </c>
+      <c r="B112">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>211</v>
+      </c>
+      <c r="B113">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>212</v>
+      </c>
+      <c r="B114">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>213</v>
+      </c>
+      <c r="B115">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>214</v>
+      </c>
+      <c r="B116">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>215</v>
+      </c>
+      <c r="B117">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>216</v>
+      </c>
+      <c r="B118">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>217</v>
+      </c>
+      <c r="B119">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>218</v>
+      </c>
+      <c r="B120">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>219</v>
+      </c>
+      <c r="B121">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>220</v>
+      </c>
+      <c r="B122">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>221</v>
+      </c>
+      <c r="B123">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>222</v>
+      </c>
+      <c r="B124">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>223</v>
+      </c>
+      <c r="B125">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>224</v>
+      </c>
+      <c r="B126">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>225</v>
+      </c>
+      <c r="B127">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>226</v>
+      </c>
+      <c r="B128">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>227</v>
+      </c>
+      <c r="B129">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>228</v>
+      </c>
+      <c r="B130">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>229</v>
+      </c>
+      <c r="B131">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>230</v>
+      </c>
+      <c r="B132">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>231</v>
+      </c>
+      <c r="B133">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>232</v>
+      </c>
+      <c r="B134">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>233</v>
+      </c>
+      <c r="B135">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>234</v>
+      </c>
+      <c r="B136">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>235</v>
+      </c>
+      <c r="B137">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>236</v>
+      </c>
+      <c r="B138">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>237</v>
+      </c>
+      <c r="B139">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>238</v>
+      </c>
+      <c r="B140">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>239</v>
+      </c>
+      <c r="B141">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>240</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>241</v>
+      </c>
+      <c r="B143">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>242</v>
+      </c>
+      <c r="B144">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>243</v>
+      </c>
+      <c r="B145">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>244</v>
+      </c>
+      <c r="B146">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>245</v>
+      </c>
+      <c r="B147">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>246</v>
+      </c>
+      <c r="B148">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>247</v>
+      </c>
+      <c r="B149">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>248</v>
+      </c>
+      <c r="B150">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>249</v>
+      </c>
+      <c r="B151">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>250</v>
+      </c>
+      <c r="B152">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>251</v>
+      </c>
+      <c r="B153">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>252</v>
+      </c>
+      <c r="B154">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>253</v>
+      </c>
+      <c r="B155">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>254</v>
+      </c>
+      <c r="B156">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>255</v>
+      </c>
+      <c r="B157">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>256</v>
+      </c>
+      <c r="B158">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>257</v>
+      </c>
+      <c r="B159">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>258</v>
+      </c>
+      <c r="B160">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>259</v>
+      </c>
+      <c r="B161">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>260</v>
+      </c>
+      <c r="B162">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>261</v>
+      </c>
+      <c r="B163">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>262</v>
+      </c>
+      <c r="B164">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>263</v>
+      </c>
+      <c r="B165">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>264</v>
+      </c>
+      <c r="B166">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>265</v>
+      </c>
+      <c r="B167">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>266</v>
+      </c>
+      <c r="B168">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>267</v>
+      </c>
+      <c r="B169">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>268</v>
+      </c>
+      <c r="B170">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>269</v>
+      </c>
+      <c r="B171">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>270</v>
+      </c>
+      <c r="B172">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>271</v>
+      </c>
+      <c r="B173">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>272</v>
+      </c>
+      <c r="B174">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>273</v>
+      </c>
+      <c r="B175">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>274</v>
+      </c>
+      <c r="B176">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>275</v>
+      </c>
+      <c r="B177">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>276</v>
+      </c>
+      <c r="B178">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>277</v>
+      </c>
+      <c r="B179">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>278</v>
+      </c>
+      <c r="B180">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>279</v>
+      </c>
+      <c r="B181">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>280</v>
+      </c>
+      <c r="B182">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>281</v>
+      </c>
+      <c r="B183">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>282</v>
+      </c>
+      <c r="B184">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>283</v>
+      </c>
+      <c r="B185">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>284</v>
+      </c>
+      <c r="B186">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>285</v>
+      </c>
+      <c r="B187">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>286</v>
+      </c>
+      <c r="B188">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>287</v>
+      </c>
+      <c r="B189">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>288</v>
+      </c>
+      <c r="B190">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>289</v>
+      </c>
+      <c r="B191">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>290</v>
+      </c>
+      <c r="B192">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>291</v>
+      </c>
+      <c r="B193">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>292</v>
+      </c>
+      <c r="B194">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>293</v>
+      </c>
+      <c r="B195">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>294</v>
+      </c>
+      <c r="B196">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>295</v>
+      </c>
+      <c r="B197">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>296</v>
+      </c>
+      <c r="B198">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>297</v>
+      </c>
+      <c r="B199">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>298</v>
+      </c>
+      <c r="B200">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>299</v>
+      </c>
+      <c r="B201">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>300</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>0</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>100</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>101</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>102</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>103</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>104</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>105</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>106</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>107</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>108</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>109</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>110</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>111</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>112</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>113</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>114</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>115</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>116</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>117</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>118</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>119</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>120</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>121</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>122</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>123</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>124</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>125</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>126</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>127</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>128</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>129</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>130</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>131</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>132</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>133</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>134</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>135</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>136</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>137</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>138</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>139</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>140</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>141</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>142</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>143</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>144</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>145</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>146</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>147</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>148</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>149</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>150</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>151</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>152</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>153</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>154</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>155</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>156</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>157</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>158</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>159</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>160</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>161</v>
+      </c>
+      <c r="B266">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>162</v>
+      </c>
+      <c r="B267">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>163</v>
+      </c>
+      <c r="B268">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>164</v>
+      </c>
+      <c r="B269">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>165</v>
+      </c>
+      <c r="B270">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>166</v>
+      </c>
+      <c r="B271">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>167</v>
+      </c>
+      <c r="B272">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>168</v>
+      </c>
+      <c r="B273">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>169</v>
+      </c>
+      <c r="B274">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>170</v>
+      </c>
+      <c r="B275">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>171</v>
+      </c>
+      <c r="B276">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>172</v>
+      </c>
+      <c r="B277">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>173</v>
+      </c>
+      <c r="B278">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>174</v>
+      </c>
+      <c r="B279">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>175</v>
+      </c>
+      <c r="B280">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>176</v>
+      </c>
+      <c r="B281">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>177</v>
+      </c>
+      <c r="B282">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>178</v>
+      </c>
+      <c r="B283">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>179</v>
+      </c>
+      <c r="B284">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>180</v>
+      </c>
+      <c r="B285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>181</v>
+      </c>
+      <c r="B286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>182</v>
+      </c>
+      <c r="B287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>183</v>
+      </c>
+      <c r="B288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>184</v>
+      </c>
+      <c r="B289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>185</v>
+      </c>
+      <c r="B290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>186</v>
+      </c>
+      <c r="B291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>187</v>
+      </c>
+      <c r="B292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>188</v>
+      </c>
+      <c r="B293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>189</v>
+      </c>
+      <c r="B294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>190</v>
+      </c>
+      <c r="B295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>191</v>
+      </c>
+      <c r="B296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>192</v>
+      </c>
+      <c r="B297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>193</v>
+      </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>194</v>
+      </c>
+      <c r="B299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>195</v>
+      </c>
+      <c r="B300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>196</v>
+      </c>
+      <c r="B301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>197</v>
+      </c>
+      <c r="B302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>198</v>
+      </c>
+      <c r="B303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>199</v>
+      </c>
+      <c r="B304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>200</v>
+      </c>
+      <c r="B305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>201</v>
+      </c>
+      <c r="B306">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>202</v>
+      </c>
+      <c r="B307">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>203</v>
+      </c>
+      <c r="B308">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>204</v>
+      </c>
+      <c r="B309">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>205</v>
+      </c>
+      <c r="B310">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>206</v>
+      </c>
+      <c r="B311">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>207</v>
+      </c>
+      <c r="B312">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>208</v>
+      </c>
+      <c r="B313">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>209</v>
+      </c>
+      <c r="B314">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>210</v>
+      </c>
+      <c r="B315">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>211</v>
+      </c>
+      <c r="B316">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>212</v>
+      </c>
+      <c r="B317">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>213</v>
+      </c>
+      <c r="B318">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>214</v>
+      </c>
+      <c r="B319">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>215</v>
+      </c>
+      <c r="B320">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>216</v>
+      </c>
+      <c r="B321">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>217</v>
+      </c>
+      <c r="B322">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>218</v>
+      </c>
+      <c r="B323">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>219</v>
+      </c>
+      <c r="B324">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>220</v>
+      </c>
+      <c r="B325">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>221</v>
+      </c>
+      <c r="B326">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>222</v>
+      </c>
+      <c r="B327">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>223</v>
+      </c>
+      <c r="B328">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>224</v>
+      </c>
+      <c r="B329">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>225</v>
+      </c>
+      <c r="B330">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>226</v>
+      </c>
+      <c r="B331">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>227</v>
+      </c>
+      <c r="B332">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>228</v>
+      </c>
+      <c r="B333">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>229</v>
+      </c>
+      <c r="B334">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>230</v>
+      </c>
+      <c r="B335">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>231</v>
+      </c>
+      <c r="B336">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>232</v>
+      </c>
+      <c r="B337">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>233</v>
+      </c>
+      <c r="B338">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>234</v>
+      </c>
+      <c r="B339">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>235</v>
+      </c>
+      <c r="B340">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>236</v>
+      </c>
+      <c r="B341">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>237</v>
+      </c>
+      <c r="B342">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>238</v>
+      </c>
+      <c r="B343">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>239</v>
+      </c>
+      <c r="B344">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>240</v>
+      </c>
+      <c r="B345">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>241</v>
+      </c>
+      <c r="B346">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>242</v>
+      </c>
+      <c r="B347">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>243</v>
+      </c>
+      <c r="B348">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>244</v>
+      </c>
+      <c r="B349">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>245</v>
+      </c>
+      <c r="B350">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>246</v>
+      </c>
+      <c r="B351">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>247</v>
+      </c>
+      <c r="B352">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>248</v>
+      </c>
+      <c r="B353">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>249</v>
+      </c>
+      <c r="B354">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>250</v>
+      </c>
+      <c r="B355">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>251</v>
+      </c>
+      <c r="B356">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>252</v>
+      </c>
+      <c r="B357">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>253</v>
+      </c>
+      <c r="B358">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>254</v>
+      </c>
+      <c r="B359">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>255</v>
+      </c>
+      <c r="B360">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>256</v>
+      </c>
+      <c r="B361">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>257</v>
+      </c>
+      <c r="B362">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>258</v>
+      </c>
+      <c r="B363">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>259</v>
+      </c>
+      <c r="B364">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>260</v>
+      </c>
+      <c r="B365">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>261</v>
+      </c>
+      <c r="B366">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>262</v>
+      </c>
+      <c r="B367">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>263</v>
+      </c>
+      <c r="B368">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>264</v>
+      </c>
+      <c r="B369">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>265</v>
+      </c>
+      <c r="B370">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>266</v>
+      </c>
+      <c r="B371">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>267</v>
+      </c>
+      <c r="B372">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>268</v>
+      </c>
+      <c r="B373">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>269</v>
+      </c>
+      <c r="B374">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>270</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>271</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>272</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>273</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>274</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>275</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>276</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>277</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>278</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>279</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>280</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>281</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>282</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>283</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>284</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>285</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>286</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>287</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>288</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>289</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>290</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>291</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>292</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>293</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>294</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>295</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>296</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>297</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>298</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>299</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>300</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" t="s">
+        <v>0</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>100</v>
+      </c>
+      <c r="B408">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>101</v>
+      </c>
+      <c r="B409">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>102</v>
+      </c>
+      <c r="B410">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>103</v>
+      </c>
+      <c r="B411">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>104</v>
+      </c>
+      <c r="B412">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>105</v>
+      </c>
+      <c r="B413">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>106</v>
+      </c>
+      <c r="B414">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>107</v>
+      </c>
+      <c r="B415">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>108</v>
+      </c>
+      <c r="B416">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>109</v>
+      </c>
+      <c r="B417">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>110</v>
+      </c>
+      <c r="B418">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>111</v>
+      </c>
+      <c r="B419">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>112</v>
+      </c>
+      <c r="B420">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>113</v>
+      </c>
+      <c r="B421">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>114</v>
+      </c>
+      <c r="B422">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>115</v>
+      </c>
+      <c r="B423">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>116</v>
+      </c>
+      <c r="B424">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>117</v>
+      </c>
+      <c r="B425">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>118</v>
+      </c>
+      <c r="B426">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>119</v>
+      </c>
+      <c r="B427">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>120</v>
+      </c>
+      <c r="B428">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>121</v>
+      </c>
+      <c r="B429">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>122</v>
+      </c>
+      <c r="B430">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>123</v>
+      </c>
+      <c r="B431">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>124</v>
+      </c>
+      <c r="B432">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>125</v>
+      </c>
+      <c r="B433">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>126</v>
+      </c>
+      <c r="B434">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>127</v>
+      </c>
+      <c r="B435">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>128</v>
+      </c>
+      <c r="B436">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>129</v>
+      </c>
+      <c r="B437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>130</v>
+      </c>
+      <c r="B438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>131</v>
+      </c>
+      <c r="B439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>132</v>
+      </c>
+      <c r="B440">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>133</v>
+      </c>
+      <c r="B441">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>134</v>
+      </c>
+      <c r="B442">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>135</v>
+      </c>
+      <c r="B443">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>136</v>
+      </c>
+      <c r="B444">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>137</v>
+      </c>
+      <c r="B445">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>138</v>
+      </c>
+      <c r="B446">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>139</v>
+      </c>
+      <c r="B447">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>140</v>
+      </c>
+      <c r="B448">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>141</v>
+      </c>
+      <c r="B449">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>142</v>
+      </c>
+      <c r="B450">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>143</v>
+      </c>
+      <c r="B451">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>144</v>
+      </c>
+      <c r="B452">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>145</v>
+      </c>
+      <c r="B453">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>146</v>
+      </c>
+      <c r="B454">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>147</v>
+      </c>
+      <c r="B455">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>148</v>
+      </c>
+      <c r="B456">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>149</v>
+      </c>
+      <c r="B457">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>150</v>
+      </c>
+      <c r="B458">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>151</v>
+      </c>
+      <c r="B459">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>152</v>
+      </c>
+      <c r="B460">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>153</v>
+      </c>
+      <c r="B461">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>154</v>
+      </c>
+      <c r="B462">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>155</v>
+      </c>
+      <c r="B463">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>156</v>
+      </c>
+      <c r="B464">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>157</v>
+      </c>
+      <c r="B465">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>158</v>
+      </c>
+      <c r="B466">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>159</v>
+      </c>
+      <c r="B467">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>160</v>
+      </c>
+      <c r="B468">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>161</v>
+      </c>
+      <c r="B469">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>162</v>
+      </c>
+      <c r="B470">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>163</v>
+      </c>
+      <c r="B471">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>164</v>
+      </c>
+      <c r="B472">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>165</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>166</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>167</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>168</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>169</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>170</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>171</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>172</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>173</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>174</v>
+      </c>
+      <c r="B482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>175</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>176</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>177</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>178</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>179</v>
+      </c>
+      <c r="B487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>180</v>
+      </c>
+      <c r="B488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>181</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>182</v>
+      </c>
+      <c r="B490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>183</v>
+      </c>
+      <c r="B491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>184</v>
+      </c>
+      <c r="B492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>185</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>186</v>
+      </c>
+      <c r="B494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>187</v>
+      </c>
+      <c r="B495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>188</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>189</v>
+      </c>
+      <c r="B497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>190</v>
+      </c>
+      <c r="B498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>191</v>
+      </c>
+      <c r="B499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>192</v>
+      </c>
+      <c r="B500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>193</v>
+      </c>
+      <c r="B501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>194</v>
+      </c>
+      <c r="B502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>195</v>
+      </c>
+      <c r="B503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>196</v>
+      </c>
+      <c r="B504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>197</v>
+      </c>
+      <c r="B505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>198</v>
+      </c>
+      <c r="B506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>199</v>
+      </c>
+      <c r="B507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>200</v>
+      </c>
+      <c r="B508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>201</v>
+      </c>
+      <c r="B509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>202</v>
+      </c>
+      <c r="B510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>203</v>
+      </c>
+      <c r="B511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>204</v>
+      </c>
+      <c r="B512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>205</v>
+      </c>
+      <c r="B513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>206</v>
+      </c>
+      <c r="B514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>207</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>208</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>209</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>210</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>211</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>212</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>213</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>214</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>215</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>216</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>217</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>218</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>219</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>220</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>221</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>222</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>223</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>224</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>225</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>226</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>227</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>228</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>229</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>230</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>231</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>232</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>233</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>234</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>235</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>236</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>237</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>238</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>239</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>240</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>241</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>242</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>243</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>244</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>245</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>246</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>247</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>248</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>249</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>250</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>251</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>252</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>253</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>254</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>255</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>256</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>257</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>258</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>259</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>260</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>261</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>262</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>263</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>264</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>265</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>266</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>267</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>268</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>269</v>
+      </c>
+      <c r="B577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>270</v>
+      </c>
+      <c r="B578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>271</v>
+      </c>
+      <c r="B579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>272</v>
+      </c>
+      <c r="B580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>273</v>
+      </c>
+      <c r="B581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>274</v>
+      </c>
+      <c r="B582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>275</v>
+      </c>
+      <c r="B583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>276</v>
+      </c>
+      <c r="B584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>277</v>
+      </c>
+      <c r="B585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>278</v>
+      </c>
+      <c r="B586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>279</v>
+      </c>
+      <c r="B587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>280</v>
+      </c>
+      <c r="B588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>281</v>
+      </c>
+      <c r="B589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>282</v>
+      </c>
+      <c r="B590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>283</v>
+      </c>
+      <c r="B591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>284</v>
+      </c>
+      <c r="B592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>285</v>
+      </c>
+      <c r="B593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>286</v>
+      </c>
+      <c r="B594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>287</v>
+      </c>
+      <c r="B595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>288</v>
+      </c>
+      <c r="B596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>289</v>
+      </c>
+      <c r="B597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>290</v>
+      </c>
+      <c r="B598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>291</v>
+      </c>
+      <c r="B599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>292</v>
+      </c>
+      <c r="B600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>293</v>
+      </c>
+      <c r="B601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>294</v>
+      </c>
+      <c r="B602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>295</v>
+      </c>
+      <c r="B603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>296</v>
+      </c>
+      <c r="B604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>297</v>
+      </c>
+      <c r="B605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>298</v>
+      </c>
+      <c r="B606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>299</v>
+      </c>
+      <c r="B607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>300</v>
+      </c>
+      <c r="B608">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
